--- a/output/full_scan/batch_seq6_2026-06-30.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-30.xlsx
@@ -527,41 +527,41 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6288</v>
+        <v>6271</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>993.7637113435804</v>
+        <v>1150.204966178548</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>24.25</v>
+        <v>267</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.34849850742816</v>
+        <v>58.81852436508834</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.41374104484789</v>
+        <v>27.17055673844052</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.476371134358034</v>
+        <v>1.664747774014457</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.196035848321791</v>
+        <v>0.3849936461737862</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6271</v>
+        <v>6191</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>930.2049661785476</v>
+        <v>1050.644951556672</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>267</v>
+        <v>106.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,29 +605,29 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>58.8185243589301</v>
+        <v>61.4484562758624</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27.17055682577154</v>
+        <v>22.67814634431744</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.664747774014457</v>
+        <v>3.1644951556672</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3849936460783851</v>
+        <v>0.8268139291606469</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>882.2570458013606</v>
+        <v>1017.25704580136</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>237</v>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.84931909697373</v>
+        <v>57.84931910118055</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>24.06567338334854</v>
+        <v>24.06567341546563</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0.9655596072720668</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.080080338351884</v>
+        <v>0.0800803383328014</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6435</v>
+        <v>6213</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>816.3379190131319</v>
+        <v>1006.095614227288</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>363.5</v>
+        <v>370.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,29 +711,29 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>69.28227858877815</v>
+        <v>72.26571633377246</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.72108388213342</v>
+        <v>20.55229051335089</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.459114809512338</v>
+        <v>1.11308717608408</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.255984855418617</v>
+        <v>10.27816789878106</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>803.8937939584472</v>
+        <v>993.8937939584472</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>124.5</v>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.41657080740823</v>
+        <v>65.41657083935783</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>35.68266417623689</v>
+        <v>35.68266418982757</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.7704011635336772</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0223234623432375</v>
+        <v>0.0223234623241452</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6446</v>
+        <v>6196</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>757.5857134532104</v>
+        <v>991.1143641071628</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1340</v>
+        <v>554</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,66 +817,66 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>82.83725562998475</v>
+        <v>60.22370172660651</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>50.58828137551408</v>
+        <v>34.5302083658745</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.639166075318903</v>
+        <v>0.9506982772622936</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>24.41462078374848</v>
+        <v>-4.629784524146473</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6175</v>
+        <v>6288</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>756.9501421026813</v>
+        <v>978.7637113435804</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>112.5</v>
+        <v>24.25</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.55049926169109</v>
+        <v>66.61319950649572</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>39.37878356519528</v>
+        <v>24.95817109940215</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5001147441071531</v>
+        <v>3.476371134358034</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.6476829875308141</v>
+        <v>0.1957001717651283</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6207</v>
+        <v>6446</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>746.5501115662704</v>
+        <v>967.6420573898732</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>146.5</v>
+        <v>1340</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.18053945221284</v>
+        <v>82.83725569821671</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>57.60005602325791</v>
+        <v>50.58828138592636</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.4420503140137703</v>
+        <v>1.6433242654414</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-3.11155249857811</v>
+        <v>24.41462077821544</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6196</v>
+        <v>6435</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>736.1143641071628</v>
+        <v>956.337919013132</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>554</v>
+        <v>363.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.22370172660651</v>
+        <v>69.28227859728879</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>34.530208573679</v>
+        <v>34.72108379230712</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.9506982772622936</v>
+        <v>2.459114809512338</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-4.629784524337285</v>
+        <v>3.25598485580014</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6168</v>
+        <v>6175</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>730.2425543819974</v>
+        <v>896.9501421026813</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>31.05</v>
+        <v>112.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>56.45812713073776</v>
+        <v>59.55049928083757</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.52796102382688</v>
+        <v>39.37878358501413</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7367969185756682</v>
+        <v>0.5001147441071531</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.2958140961519833</v>
+        <v>-0.6476829875117378</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6191</v>
+        <v>6409</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>690.644951556672</v>
+        <v>885.5007100822379</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>106.5</v>
+        <v>1085</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.44845624070847</v>
+        <v>72.69580511324732</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.67814633782752</v>
+        <v>43.35171351576548</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.1644951556672</v>
+        <v>1.350799589451031</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.826813929103411</v>
+        <v>12.96176718567984</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6209</v>
+        <v>6239</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>687.645523483182</v>
+        <v>825.7036637909</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>80.7</v>
+        <v>337.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>46.65009956106766</v>
+        <v>54.52526699572456</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35.17476877796158</v>
+        <v>27.83418948715953</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.1830010788665222</v>
+        <v>0.7051190750628047</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.837952191694241</v>
+        <v>-6.112828140789677</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6259</v>
+        <v>6182</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>685.6527958736355</v>
+        <v>824.6043415534573</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>35.8</v>
+        <v>123</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.93639524406419</v>
+        <v>66.63295219541146</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45.47536482384715</v>
+        <v>39.35747504834411</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.353658720893418</v>
+        <v>0.4797632153659441</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.4077569356963106</v>
+        <v>0.3937610748888911</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6411</v>
+        <v>6432</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>681.4263088640395</v>
+        <v>810.0836699615538</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>99.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>51.73230568633328</v>
+        <v>55.71207293822801</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27.66645474737851</v>
+        <v>37.6586592408843</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.370151856888662</v>
+        <v>0.902202375612242</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.8311314006496229</v>
+        <v>-1.112328198584554</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6208</v>
+        <v>6270</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>673.5373331422016</v>
+        <v>802.2169044990288</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>97</v>
+        <v>38.95</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>53.71269470849723</v>
+        <v>61.83359967227079</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.37783397854697</v>
+        <v>51.68099966279832</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.804351516757874</v>
+        <v>0.3886461014182802</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.3228361814185843</v>
+        <v>0.2062885176981517</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6432</v>
+        <v>6259</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>670.0836699615538</v>
+        <v>800.6527958736355</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>35.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>55.71207293069352</v>
+        <v>57.93639524506504</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>37.65865921301288</v>
+        <v>45.47536482061996</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.902202375612242</v>
+        <v>1.353658720893418</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.112328198536837</v>
+        <v>0.407756935744008</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6270</v>
+        <v>6214</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>662.2169044990288</v>
+        <v>790.8685662063357</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>38.95</v>
+        <v>134</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,29 +1400,29 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>61.83359965775366</v>
+        <v>48.66724017966808</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>51.68099966279831</v>
+        <v>20.42823635903485</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3886461014182802</v>
+        <v>0.8663548283211662</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.2062885177172253</v>
+        <v>-1.987516192047068</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>659.5279422592481</v>
+        <v>784.5279422592481</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>65.09999999999999</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.47996666583099</v>
+        <v>54.47996667985861</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.99395408654981</v>
+        <v>28.99395408654982</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.4421936314212628</v>
@@ -1465,17 +1465,17 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0595008746446419</v>
+        <v>0.0595008746732612</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>657.7648851581793</v>
+        <v>772.7648851581793</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>50.2</v>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>44.08922807410845</v>
+        <v>44.08922814803224</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21.56418745393159</v>
+        <v>21.5641873184606</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.198856511930989</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.755502798459835</v>
+        <v>-0.7555027986315522</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6182</v>
+        <v>6285</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>654.6043415534573</v>
+        <v>767.9875600219658</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>123</v>
+        <v>259.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>66.63295219063247</v>
+        <v>47.16322934220242</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>39.35747515489279</v>
+        <v>21.11997305300599</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4797632153659441</v>
+        <v>0.7346401436964454</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3937610749461271</v>
+        <v>-4.319044937662829</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6213</v>
+        <v>6190</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>616.0956142272884</v>
+        <v>755.0846133697537</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>370.5</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>72.26571633685857</v>
+        <v>56.27710906790772</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.552290616067</v>
+        <v>20.12501395097379</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.11308717608408</v>
+        <v>1.082932300211204</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>10.27816789817051</v>
+        <v>-0.1734244894456131</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6190</v>
+        <v>6207</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>615.0846133697537</v>
+        <v>746.5501115662704</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>84</v>
+        <v>146.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.27710907763648</v>
+        <v>57.18053946575806</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>20.12501394466348</v>
+        <v>57.60005604643838</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.082932300211204</v>
+        <v>0.4420503140137703</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1734244894933192</v>
+        <v>-3.111552498673531</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6223</v>
+        <v>6292</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>607.1486228745256</v>
+        <v>744.6490095165699</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>6090</v>
+        <v>62.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>48.98191135935552</v>
+        <v>53.29376478753955</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.04041965945494</v>
+        <v>27.03094008713829</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9264817671739952</v>
+        <v>0.5409332573832206</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-57.25564513664688</v>
+        <v>-0.9422341255881328</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6292</v>
+        <v>6278</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>604.6490095165699</v>
+        <v>743.3689269773187</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>62.3</v>
+        <v>213</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.29376477905178</v>
+        <v>55.41921789978397</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.03094008713829</v>
+        <v>18.29538216781696</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5409332573832206</v>
+        <v>1.268174704529838</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.9422341255690572</v>
+        <v>-1.417223752018386</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6239</v>
+        <v>6168</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>590.7036637909</v>
+        <v>715.2425543819974</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>337.5</v>
+        <v>31.05</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.52526698276891</v>
+        <v>56.45812713729691</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>27.83418955473543</v>
+        <v>26.52796097731406</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7051190750628047</v>
+        <v>0.7367969185756682</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-6.112828140694305</v>
+        <v>0.2958140961710609</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6265</v>
+        <v>6197</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>587.077843946837</v>
+        <v>700.5608707351741</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>53.4</v>
+        <v>350</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>48.76090569334986</v>
+        <v>61.89932662901871</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.1486315102422</v>
+        <v>43.64763018028975</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.1770979133691197</v>
+        <v>0.3883745029311274</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.119723371976104</v>
+        <v>-2.345812862425316</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6197</v>
+        <v>6209</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>585.5608707351741</v>
+        <v>687.645523483182</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>350</v>
+        <v>80.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>61.89932657105902</v>
+        <v>46.65009957047455</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>43.64763016785096</v>
+        <v>35.17476877264568</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.3883745029311274</v>
+        <v>0.1830010788665222</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-2.345812861280596</v>
+        <v>-1.837952191694241</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6409</v>
+        <v>6411</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>570.5007100822379</v>
+        <v>681.4263088640395</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1085</v>
+        <v>99.2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>72.69580507799274</v>
+        <v>51.73230569769072</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>43.35171342729316</v>
+        <v>27.66645471367845</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.350799589451031</v>
+        <v>0.370151856888662</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>12.96176718663384</v>
+        <v>-0.8311314007259316</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6217</v>
+        <v>6438</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>565.9711734338536</v>
+        <v>680.4215118992776</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>256</v>
+        <v>157.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>49.66305909438452</v>
+        <v>50.55429749982272</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14.33695861109798</v>
+        <v>23.69785561891022</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6239860998730513</v>
+        <v>0.9295460436295968</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2215758206924851</v>
+        <v>0.7254984316299549</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6449</v>
+        <v>6208</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>555.4335807384399</v>
+        <v>673.5373331422016</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>345</v>
+        <v>97</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>47.23833500984559</v>
+        <v>53.71269471985831</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>29.3397848381134</v>
+        <v>20.37783393797519</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.314614650228191</v>
+        <v>0.804351516757874</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-15.45819433872125</v>
+        <v>0.3228361814567555</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6472</v>
+        <v>6284</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>541.7767163603144</v>
+        <v>663.8821725269987</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>422</v>
+        <v>100.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>55.61881939822162</v>
+        <v>50.27724006618109</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.22930931906573</v>
+        <v>34.57179364070333</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.907446326491488</v>
+        <v>0.356203866993456</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>3.154904090197697</v>
+        <v>-1.321533493271077</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6177</v>
+        <v>6174</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>528.5969072326328</v>
+        <v>663.43746039753</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45.1</v>
+        <v>49.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.3009495388955</v>
+        <v>53.63452304261172</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.27913577871629</v>
+        <v>36.5138002056437</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5037310209359205</v>
+        <v>0.3982041081631613</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1992271783886224</v>
+        <v>-0.6446280221422054</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6269</v>
+        <v>6246</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>525.8042358694515</v>
+        <v>657.005268608362</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>71</v>
+        <v>16.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>49.28437960551981</v>
+        <v>55.10415512978542</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>28.708333712977</v>
+        <v>24.72843640413497</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4804235869451458</v>
+        <v>1.000526860836208</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.9836120876783272</v>
+        <v>0.1177429426134374</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>523.4374603975301</v>
+        <v>643.5969072326328</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>49.8</v>
+        <v>45.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.63452302884536</v>
+        <v>46.30094959745204</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>36.51380022058349</v>
+        <v>20.27913592105585</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3982041081631613</v>
+        <v>0.5037310209359205</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.644628022104047</v>
+        <v>-0.1992271787511292</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6405</v>
+        <v>6217</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>517.0847685207309</v>
+        <v>640.9711734338534</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>61.3</v>
+        <v>256</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.5810390648671</v>
+        <v>49.66305909598193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.73522098312623</v>
+        <v>14.33695864876022</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5000303502005272</v>
+        <v>0.6239860998730513</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.707265143090666</v>
+        <v>0.2215758207210103</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6465</v>
+        <v>6234</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>516.9021183997914</v>
+        <v>613.5326452844737</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>61.6</v>
+        <v>48.6</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.44345692589382</v>
+        <v>53.81254537020155</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.40827648052034</v>
+        <v>13.90422991159719</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2715498554329559</v>
+        <v>1.428797211682578</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.5324495439003014</v>
+        <v>0.2637066373983192</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6274</v>
+        <v>6223</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>516.0973674932125</v>
+        <v>607.1723516093762</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1680</v>
+        <v>6090</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.84352081795416</v>
+        <v>48.98191136360648</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>26.75734239887309</v>
+        <v>22.04041976386752</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8255040191416356</v>
+        <v>0.9281874884944294</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-21.48563912379586</v>
+        <v>-57.25564513741011</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6285</v>
+        <v>6261</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>507.9875600219659</v>
+        <v>591.5807222739759</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>259.5</v>
+        <v>93.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.16322931915648</v>
+        <v>41.29886777677265</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.11997301241732</v>
+        <v>21.14714444630131</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7346401436964454</v>
+        <v>0.3310570531356941</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-4.319044937567412</v>
+        <v>-0.7111124161371261</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6451</v>
+        <v>6185</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>503.9910133642651</v>
+        <v>590.1075299871495</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>568</v>
+        <v>14.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>49.86516392561859</v>
+        <v>51.80817920712541</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>31.50586423639913</v>
+        <v>16.64497664775838</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5791474615363918</v>
+        <v>0.620356259194261</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-4.787072785695067</v>
+        <v>-0.0049466569447017</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6282</v>
+        <v>6265</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>497.1457194258025</v>
+        <v>587.077843946837</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>58.2</v>
+        <v>53.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.05857360008581</v>
+        <v>48.76090569907771</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27.27020204582015</v>
+        <v>28.14863151622382</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3940608956050446</v>
+        <v>0.1770979133691197</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.7989235064082489</v>
+        <v>-1.119723371993282</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6246</v>
+        <v>6263</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>487.0052686083621</v>
+        <v>576.1227898745718</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>16.1</v>
+        <v>163</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.10415502328202</v>
+        <v>49.08613836755601</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.72843638771732</v>
+        <v>13.36833703958556</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.000526860836208</v>
+        <v>0.4085748259745045</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1177429426897542</v>
+        <v>-0.6185103941009004</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6275</v>
+        <v>6227</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>485.889993048202</v>
+        <v>572.9580447377569</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>49.65</v>
+        <v>121.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.04300512483284</v>
+        <v>50.22682679053077</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16.61069387193286</v>
+        <v>17.06906415932504</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.503072077527177</v>
+        <v>0.3978079514071663</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0997735345636344</v>
+        <v>-1.728611180400336</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6220</v>
+        <v>6412</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>483.7846191481033</v>
+        <v>568.7780274039991</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>33.65</v>
+        <v>95.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>44.76356116148299</v>
+        <v>53.14024813158756</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>51.81788431924357</v>
+        <v>16.36288293573874</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8695862039129122</v>
+        <v>0.7229851671146679</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.3554445099525085</v>
+        <v>-0.3006208138838665</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6419</v>
+        <v>6192</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>481.3407995982355</v>
+        <v>567.6985225501522</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>143.5</v>
+        <v>123</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.69462315736412</v>
+        <v>50.90114726272748</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.12853698506726</v>
+        <v>21.22517907947432</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2560701074523542</v>
+        <v>0.3974088052774792</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.3547703071273922</v>
+        <v>0.1912749204385773</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6185</v>
+        <v>6233</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>475.1075299871495</v>
+        <v>560.4912045954051</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>14.3</v>
+        <v>25.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.80817889116105</v>
+        <v>51.26912062858351</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.64497664775837</v>
+        <v>13.93652441179765</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.620356259194261</v>
+        <v>0.4774881704094067</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0049466569447017</v>
+        <v>0.2061248169032711</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6166</v>
+        <v>6464</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>469.7233457110664</v>
+        <v>551.2047732328015</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>139.5</v>
+        <v>78</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>54.8314382916973</v>
+        <v>56.70008416463498</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>56.87448802541152</v>
+        <v>18.93451056259745</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5282957499841627</v>
+        <v>4.579743938739118</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.926258212452282</v>
+        <v>-0.0546490539594568</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6279</v>
+        <v>6414</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>463.7165272815584</v>
+        <v>545.7406953980334</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>117.5</v>
+        <v>369.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.37485386070733</v>
+        <v>51.00326513001544</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15.52280656566675</v>
+        <v>19.31171129096956</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4094322663028553</v>
+        <v>0.6985136384467651</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.6361823596100832</v>
+        <v>-3.877210911394601</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6278</v>
+        <v>6449</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>458.3689269773186</v>
+        <v>545.4335807384399</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>213</v>
+        <v>345</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.41921789009961</v>
+        <v>47.23833501070337</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.29538216083939</v>
+        <v>29.33978472050146</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.268174704529838</v>
+        <v>1.314614650228191</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.417223751923014</v>
+        <v>-15.45819433832062</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6229</v>
+        <v>6228</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>444.1576206166678</v>
+        <v>543.257791211473</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>26.55</v>
+        <v>19.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.54029430574631</v>
+        <v>45.94908305583448</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>12.3704925202512</v>
+        <v>4.161386676584499</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.44377801808718</v>
+        <v>1.063358019470022</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0740109710132997</v>
+        <v>-0.11552258721916</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6164</v>
+        <v>6244</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>438.9762946327916</v>
+        <v>542.9544644339965</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>13.15</v>
+        <v>27.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>53.11899967529998</v>
+        <v>46.37571824048568</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.99263873857674</v>
+        <v>14.94390628954459</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6672482438801496</v>
+        <v>0.3133453749270888</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.047062759479977</v>
+        <v>-0.3402531017029448</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6284</v>
+        <v>6291</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>438.8821725269988</v>
+        <v>538.5686808805557</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>100.5</v>
+        <v>575</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.27724004728243</v>
+        <v>52.01687426676349</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>34.57179367883438</v>
+        <v>17.20579371354437</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.356203866993456</v>
+        <v>2.544708694669127</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.321533493366473</v>
+        <v>0.6857102574973961</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6414</v>
+        <v>6290</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>435.7406953980334</v>
+        <v>535.2452713638535</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>369.5</v>
+        <v>308.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.00326511238789</v>
+        <v>50.74179059526173</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.31171129600189</v>
+        <v>13.00097102921582</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6985136384467651</v>
+        <v>0.5338623023934794</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-3.877210911585386</v>
+        <v>-2.959721652972727</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6237</v>
+        <v>6462</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>434.3478059825956</v>
+        <v>532.0639150257007</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>44.7</v>
+        <v>117.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45.26131701923977</v>
+        <v>47.84462730466491</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.70280007901946</v>
+        <v>18.85239851343166</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2917786848871165</v>
+        <v>0.3279122807654652</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.361239968132314</v>
+        <v>0.5148697769321178</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6438</v>
+        <v>6472</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>430.4215118992775</v>
+        <v>531.7767163603146</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>157.5</v>
+        <v>422</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.55429760236498</v>
+        <v>55.61881948199778</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>23.69785561243105</v>
+        <v>26.22930934400958</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9295460436295968</v>
+        <v>0.907446326491488</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.7254984299128031</v>
+        <v>3.154904089052899</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6192</v>
+        <v>6269</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>427.6985225501522</v>
+        <v>525.8042358694515</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.901147231266</v>
+        <v>49.2843795981154</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.22517907947432</v>
+        <v>28.70833370634258</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3974088052774792</v>
+        <v>0.4804235869451458</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1912749204576489</v>
+        <v>-0.9836120876210912</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6233</v>
+        <v>6167</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>420.4912045954051</v>
+        <v>518.6247527338967</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>25.5</v>
+        <v>12.2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.26912045955235</v>
+        <v>53.203053927521</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.9365244088729</v>
+        <v>10.49627586297443</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4774881704094067</v>
+        <v>1.331779086425877</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.2061248169509702</v>
+        <v>0.0409065558219924</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6462</v>
+        <v>6405</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>417.0639150257006</v>
+        <v>517.0847685207309</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>117.5</v>
+        <v>61.3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.84462720642812</v>
+        <v>44.58103908161099</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.85239853821076</v>
+        <v>23.73522104387231</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3279122807654652</v>
+        <v>0.5000303502005272</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.5148697768939561</v>
+        <v>-1.707265143176531</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6214</v>
+        <v>6465</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>415.8685662063357</v>
+        <v>516.9021183997914</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>134</v>
+        <v>61.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.66724022195197</v>
+        <v>53.44345694809692</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.42823634231174</v>
+        <v>32.40827646977331</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8663548283211662</v>
+        <v>0.2715498554329559</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.987516191570092</v>
+        <v>-0.5324495439003014</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6227</v>
+        <v>6274</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>412.958044737757</v>
+        <v>516.0973674932126</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>121.5</v>
+        <v>1680</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,49 +3626,49 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.22682675557392</v>
+        <v>54.84352082181338</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.06906419519789</v>
+        <v>26.75734235677206</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3978079514071663</v>
+        <v>0.8255040191416356</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.728611180629286</v>
+        <v>-21.48563912331886</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6206</v>
+        <v>6423</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>407.4033355182578</v>
+        <v>513.0291878554279</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>129</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.47229043185676</v>
+        <v>41.46415035850493</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.24808399380716</v>
+        <v>28.08142502570031</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4080571561560095</v>
+        <v>0.7902034952745733</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.351813380677384</v>
+        <v>0.4708448161749849</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6261</v>
+        <v>6224</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>406.5807222739759</v>
+        <v>509.5528619621131</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>93.5</v>
+        <v>77.2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>41.29886778248801</v>
+        <v>49.19265085772092</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21.14714443296483</v>
+        <v>19.49724114467816</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3310570531356941</v>
+        <v>0.7042976043795778</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.711112416251614</v>
+        <v>-1.142814468389322</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6263</v>
+        <v>6451</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>406.1227898745718</v>
+        <v>503.9910133642651</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>163</v>
+        <v>568</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.08613832378492</v>
+        <v>49.86516392648586</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13.36833702941757</v>
+        <v>31.50586423670727</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4085748259745045</v>
+        <v>0.5791474615363918</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.618510394005493</v>
+        <v>-4.787072785504268</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6244</v>
+        <v>6220</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>402.9544644339965</v>
+        <v>503.7846191481032</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>27.7</v>
+        <v>33.65</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46.37571822406688</v>
+        <v>44.76356116551735</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.94390635567492</v>
+        <v>51.81788434029274</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3133453749270888</v>
+        <v>0.8695862039129122</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.3402531016934036</v>
+        <v>-0.3554445099906702</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6176</v>
+        <v>6282</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>398.0814115444076</v>
+        <v>497.1457194258025</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>87</v>
+        <v>58.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>34.10365883616105</v>
+        <v>50.0585736010533</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.4572127930196</v>
+        <v>27.27020197745904</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7078503130143174</v>
+        <v>0.3940608956050446</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1996001817027228</v>
+        <v>-0.7989235063796301</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6290</v>
+        <v>6245</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>395.2452713638535</v>
+        <v>487.4768200155261</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>308.5</v>
+        <v>82.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,49 +3944,49 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.74179056716636</v>
+        <v>49.85163718611743</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.00097112546029</v>
+        <v>17.62617608699308</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5338623023934794</v>
+        <v>0.6271544231682228</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-2.959721652724687</v>
+        <v>-0.4587362828045409</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6225</v>
+        <v>6275</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>391.9680668676193</v>
+        <v>485.8899930482021</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>20.35</v>
+        <v>49.65</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>39.54679718142988</v>
+        <v>51.043005254066</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12.12660657588019</v>
+        <v>16.61069385833688</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.777949683065661</v>
+        <v>0.503072077527177</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.3599393482911661</v>
+        <v>0.0997735345827149</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6167</v>
+        <v>6419</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>378.6247527338966</v>
+        <v>481.3407995982355</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>12.2</v>
+        <v>143.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.20305387894881</v>
+        <v>49.69462323038603</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.49627580090046</v>
+        <v>12.12853693933832</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.331779086425877</v>
+        <v>0.2560701074523542</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0409065557892929</v>
+        <v>-0.3547703077379445</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6423</v>
+        <v>6277</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>373.0291878554281</v>
+        <v>478.3707793962725</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.46415026940904</v>
+        <v>39.976300953017</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>28.08142500406107</v>
+        <v>29.75557681933012</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7902034952745733</v>
+        <v>0.2670627668033409</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.4708448165756582</v>
+        <v>-0.6417117762477822</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6291</v>
+        <v>6166</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>368.5686808805556</v>
+        <v>469.7233457110664</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>575</v>
+        <v>139.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.01687426445322</v>
+        <v>54.83143830317886</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.2057936967265</v>
+        <v>56.87448802541152</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.544708694669127</v>
+        <v>0.5282957499841627</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.6857102576119054</v>
+        <v>-1.926258212490456</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6224</v>
+        <v>6279</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>364.5528619621131</v>
+        <v>463.7165272815584</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>77.2</v>
+        <v>117.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.19265083512735</v>
+        <v>47.37485404070779</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.49724110561292</v>
+        <v>15.52280663533707</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7042976043795778</v>
+        <v>0.4094322663028553</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.142814468274844</v>
+        <v>-0.6361823600870828</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6416</v>
+        <v>6170</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>356.7011486849694</v>
+        <v>461.7185089807169</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>52.3</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>38.35118758835885</v>
+        <v>52.82528957518191</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>23.12308052259696</v>
+        <v>15.19177113895897</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7051650110719005</v>
+        <v>0.6266925592653397</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.5604099099489988</v>
+        <v>-0.0466067719945483</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6442</v>
+        <v>6222</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>351.3604974162064</v>
+        <v>446.7204103972518</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1640</v>
+        <v>20.55</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>39.66497549460485</v>
+        <v>46.66112198057732</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11.77423947980048</v>
+        <v>27.71873583724606</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8452132603974351</v>
+        <v>1.734331253460456</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-35.06471795767436</v>
+        <v>0.0500931842830062</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6426</v>
+        <v>6229</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>349.7943310852667</v>
+        <v>444.1576206166678</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>192</v>
+        <v>26.55</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.056163223348</v>
+        <v>47.54029444356897</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.95642078846995</v>
+        <v>12.37049249077107</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4191027846774263</v>
+        <v>0.44377801808718</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.861872759764214</v>
+        <v>-0.0740109710419206</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6218</v>
+        <v>6164</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>343.8067627661826</v>
+        <v>438.9762946327916</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>36.8</v>
+        <v>13.15</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.53326378009812</v>
+        <v>53.11899966118088</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.45246575815429</v>
+        <v>22.99263883757628</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.323893048817252</v>
+        <v>0.6672482438801496</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.2691427620524932</v>
+        <v>-0.0470627594418182</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6277</v>
+        <v>6477</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>343.3707793962724</v>
+        <v>437.6488105229192</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>33.4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>39.97630087753513</v>
+        <v>53.21312254346842</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>29.75557685097296</v>
+        <v>14.43114820963264</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2670627668033409</v>
+        <v>2.325637456670941</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.6417117761523938</v>
+        <v>-0.0466436444548729</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6215</v>
+        <v>6237</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>336.6473840035481</v>
+        <v>434.3478059825956</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>103.5</v>
+        <v>44.7</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>40.59976273499837</v>
+        <v>45.26131705561846</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.53619094911346</v>
+        <v>17.70280011235648</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3029169002183844</v>
+        <v>0.2917786848871165</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.8202383042520345</v>
+        <v>-0.3612399681513935</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6234</v>
+        <v>6206</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>333.5326452844737</v>
+        <v>427.4033355182578</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>48.6</v>
+        <v>129</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.81254536153163</v>
+        <v>47.4722905770683</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.9042299119839</v>
+        <v>16.24808399380716</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.428797211682578</v>
+        <v>0.4080571561560095</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.2637066373983192</v>
+        <v>-1.351813380963557</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6222</v>
+        <v>6417</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>331.7204103972518</v>
+        <v>414.3996660855303</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>20.55</v>
+        <v>132</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.66112194539117</v>
+        <v>49.84454089557294</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>27.71873585390869</v>
+        <v>12.88253680731954</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.734331253460456</v>
+        <v>0.3955217876067541</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0500931843211689</v>
+        <v>-0.6754909472770668</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6412</v>
+        <v>6216</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>313.7780274039991</v>
+        <v>411.9291554506814</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>95.3</v>
+        <v>22.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>53.14024799707679</v>
+        <v>46.71296612156682</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.36288289826577</v>
+        <v>15.87776852768991</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7229851671146679</v>
+        <v>0.3043690459055485</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.300620812643701</v>
+        <v>-0.0033906293454799</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6464</v>
+        <v>6176</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>312.9647587289282</v>
+        <v>398.0814115444076</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>56.70008408835052</v>
+        <v>34.10365890074084</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.93451055997077</v>
+        <v>23.4572127930196</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2557424883517891</v>
+        <v>0.7078503130143174</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0546490539403806</v>
+        <v>-0.1996001817027228</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6485</v>
+        <v>6225</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>305.3369476737118</v>
+        <v>391.9680668676193</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>20.35</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.15457633657787</v>
+        <v>39.54679723751023</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.71259004138753</v>
+        <v>12.12660674129843</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.1467057190593133</v>
+        <v>1.777949683065661</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-1.391222791101189</v>
+        <v>-0.3599393483674842</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6216</v>
+        <v>6418</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>296.9291554506814</v>
+        <v>372.0785891163889</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>22.7</v>
+        <v>31</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.71296608010633</v>
+        <v>47.88284181929637</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.87776843644821</v>
+        <v>19.75080765989063</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3043690459055485</v>
+        <v>0.2255620427080883</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0033906293550206</v>
+        <v>-0.1650979964455248</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6266</v>
+        <v>6442</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>295.4072317561827</v>
+        <v>366.3604974162064</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>24.7</v>
+        <v>1640</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>30.00906446034436</v>
+        <v>39.66497550367558</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>25.48808521098812</v>
+        <v>11.77423943370202</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.3328913002840752</v>
+        <v>0.8452132603974351</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.1387754526869403</v>
+        <v>-35.06471795490769</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6228</v>
+        <v>6183</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>293.25779121148</v>
+        <v>362.3509317641735</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>19.7</v>
+        <v>89.3</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45.94908292411655</v>
+        <v>41.84860458386827</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>4.161386514275662</v>
+        <v>12.94119797685956</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.063358019470022</v>
+        <v>0.3990696269445703</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1155225868184881</v>
+        <v>0.0070932892039075</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6417</v>
+        <v>6416</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>274.3996660855303</v>
+        <v>356.7011486849694</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>132</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>49.84454082650424</v>
+        <v>38.35118766958347</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.88253680731954</v>
+        <v>23.12308054312257</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3955217876067541</v>
+        <v>0.7051650110719005</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.6754909472770668</v>
+        <v>-0.5604099100444004</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6283</v>
+        <v>6215</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>252.7873136677137</v>
+        <v>356.647384003548</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>23.35</v>
+        <v>103.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.35546788169895</v>
+        <v>40.59976278255116</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.28293311618722</v>
+        <v>21.53619101740986</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2988002420250916</v>
+        <v>0.3029169002183844</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1484036392086945</v>
+        <v>-0.8202383046717761</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6170</v>
+        <v>6276</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>246.7185089807168</v>
+        <v>351.9010769943496</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>52.3</v>
+        <v>23</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.82528942738163</v>
+        <v>38.18382192000073</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.19177105576337</v>
+        <v>28.29271497029159</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6266925592653397</v>
+        <v>2.662892300205519</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0466067719659276</v>
+        <v>-0.1381682774128685</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6205</v>
+        <v>6426</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>241.051756139073</v>
+        <v>349.7943310852667</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>74.8</v>
+        <v>192</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.97549679306064</v>
+        <v>39.05616323605562</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.44325795047745</v>
+        <v>16.95642077667534</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2010316587086233</v>
+        <v>0.4191027846774263</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-1.090709930181022</v>
+        <v>-1.861872760279342</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6230</v>
+        <v>6188</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>239.1913756282153</v>
+        <v>349.6689637588503</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>124</v>
+        <v>77.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>37.11040654058704</v>
+        <v>43.61617295536549</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.31284859062548</v>
+        <v>17.26497212253458</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5236205657989259</v>
+        <v>1.229193234995489</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.8773464925246248</v>
+        <v>-0.3383747169834339</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6272</v>
+        <v>6218</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>238.6178586457764</v>
+        <v>343.8067627661826</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>30.8</v>
+        <v>36.8</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>35.6942152716651</v>
+        <v>49.53326380094069</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>24.50351880818757</v>
+        <v>15.45246579596592</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2427918982077313</v>
+        <v>0.323893048817252</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.4839284036739777</v>
+        <v>0.269142762004792</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6477</v>
+        <v>6198</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>237.6488105229192</v>
+        <v>333.9660803247344</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>33.4</v>
+        <v>20.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>53.21312250296965</v>
+        <v>50.90800401906495</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.43114826642988</v>
+        <v>6.552988802904613</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2.325637456670941</v>
+        <v>0.3500649808120632</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0466436443785561</v>
+        <v>0.1674736281930774</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, williams_r_recovery, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6276</v>
+        <v>6474</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>236.9010769943493</v>
+        <v>323.1939454614597</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>38.18382176475316</v>
+        <v>50.78123802491793</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>28.29271489999015</v>
+        <v>14.62104908026416</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2.662892300205519</v>
+        <v>0.3012425867825774</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1381682771457568</v>
+        <v>0.4012394321200649</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6245</v>
+        <v>6485</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>232.4768200155261</v>
+        <v>305.3369476737118</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>82.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.85163711318358</v>
+        <v>40.15457634887005</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.62617607721233</v>
+        <v>17.71258997810894</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6271544231682228</v>
+        <v>0.1467057190593133</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,48 +5446,48 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.4587362826328276</v>
+        <v>-1.391222791024871</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6183</v>
+        <v>6287</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>元隆</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>227.3509317641735</v>
+        <v>295.7768966852161</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>89.3</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G95" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>41.84860439263365</v>
+        <v>98.7048986771521</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.94119795948967</v>
+        <v>62.14969914549634</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3990696269445703</v>
+        <v>0.3819364013941486</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0070932890703339</v>
+        <v>-0.2650148572206705</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6184</v>
+        <v>6266</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>224.4355134549741</v>
+        <v>295.4072317561828</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>43.5</v>
+        <v>24.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>21.37846465081215</v>
+        <v>30.00906456185979</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>31.01218627481613</v>
+        <v>25.48808522884938</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.106923354565835</v>
+        <v>0.3328913002840752</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.366209721688283</v>
+        <v>-0.1387754527060193</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6198</v>
+        <v>6235</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>218.9660803247344</v>
+        <v>280.3589344945352</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>20.5</v>
+        <v>40.1</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.90800403484929</v>
+        <v>43.72147011022215</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>6.552988701158789</v>
+        <v>12.56761740680307</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3500649808120632</v>
+        <v>0.4908571200501366</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.167473628116758</v>
+        <v>-0.1337126342044358</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6210</v>
+        <v>6165</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>214.0049156653676</v>
+        <v>272.5738896018755</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>19.95</v>
+        <v>47.55</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>38.71551874837615</v>
+        <v>45.52981621487679</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.37858073426216</v>
+        <v>13.67076631558285</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8183449374304003</v>
+        <v>0.3356157526025841</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1250774796916558</v>
+        <v>-0.1578491511862972</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6418</v>
+        <v>6281</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>212.0785891163889</v>
+        <v>267.3454846928305</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>31</v>
+        <v>51.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.88284167056226</v>
+        <v>48.54898591905299</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.75080768247356</v>
+        <v>10.16182796380261</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2255620427080883</v>
+        <v>0.4862036186731163</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1650979963882835</v>
+        <v>-0.0041794609725346</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6443</v>
+        <v>6230</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>210.1150691429271</v>
+        <v>259.1913756282153</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>35.45</v>
+        <v>124</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.0744489055237</v>
+        <v>37.1104065895175</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.17905483469514</v>
+        <v>13.31284859062548</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.2253195721106099</v>
+        <v>0.5236205657989259</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.5786491187125726</v>
+        <v>-0.8773464928108456</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6474</v>
+        <v>6470</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>208.1939454614597</v>
+        <v>253.7134342329728</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>37</v>
+        <v>48.9</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>50.78123802491793</v>
+        <v>48.6122761346876</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14.62104908026416</v>
+        <v>13.5861900833111</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3012425867825774</v>
+        <v>0.3112790774087396</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.4012394321200649</v>
+        <v>-0.1076365664035874</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6456</v>
+        <v>6201</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>174.3404254651726</v>
+        <v>253.2713604023377</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.5</v>
+        <v>48.05</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.06543944653149</v>
+        <v>46.85069148971949</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>12.72017126734045</v>
+        <v>14.45050579288093</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.465397553291956</v>
+        <v>0.5444366412684295</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.8763030479177908</v>
+        <v>0.09408103816833591</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6235</v>
+        <v>6283</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>165.3589344945352</v>
+        <v>252.7873136677137</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>40.1</v>
+        <v>23.35</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.72147003615797</v>
+        <v>44.35546800170703</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.56761738079126</v>
+        <v>15.28293319795035</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4908571200501366</v>
+        <v>0.2988002420250916</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,51 +5923,51 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1337126342044358</v>
+        <v>-0.1484036392754686</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6287</v>
+        <v>6205</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>140.9534885758308</v>
+        <v>241.051756139073</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G104" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>8.266070145626728</v>
+        <v>42.97549681429017</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1.301832903866782</v>
+        <v>12.44325795880499</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>0.2010316587086233</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0029515679732779</v>
+        <v>-1.090709930266881</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6470</v>
+        <v>6272</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>138.7134342329728</v>
+        <v>238.6178586457764</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>48.9</v>
+        <v>30.8</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.61227605126795</v>
+        <v>35.69421563186509</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.58619005924141</v>
+        <v>24.50351884780164</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3112790774087396</v>
+        <v>0.2427918982077313</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1076365664226658</v>
+        <v>-0.4839284036262786</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6201</v>
+        <v>6184</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>138.2713604023377</v>
+        <v>224.435513454976</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>48.05</v>
+        <v>43.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.85069146390444</v>
+        <v>21.37846460094393</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.45050582882231</v>
+        <v>31.01218630567971</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5444366412684295</v>
+        <v>1.106923354565835</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.09408103820649361</v>
+        <v>-0.3662097216310418</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6188</v>
+        <v>6210</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>124.6689637588502</v>
+        <v>214.0049156653676</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>77.5</v>
+        <v>19.95</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>43.61617291361111</v>
+        <v>38.71552630636657</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.26497214460688</v>
+        <v>17.37858552389213</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.229193234995489</v>
+        <v>0.8183449374304003</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.3383747170024966</v>
+        <v>-0.1250774831641125</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6165</v>
+        <v>6443</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>112.5738896018755</v>
+        <v>210.1150691429271</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>47.55</v>
+        <v>35.45</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45.52981626574442</v>
+        <v>39.07444891765292</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.67076623276607</v>
+        <v>16.17905478574643</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3356157526025841</v>
+        <v>0.2253195721106099</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1578491512626158</v>
+        <v>-0.5786491187507292</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6281</v>
+        <v>6194</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>107.3454846928305</v>
+        <v>201.576425765718</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>51.2</v>
+        <v>32.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.54898586720465</v>
+        <v>43.7989118520876</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.16182803122762</v>
+        <v>12.7776390732192</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4862036186731163</v>
+        <v>0.3361047519028534</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0041794609725346</v>
+        <v>-0.06317393555526001</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6236</v>
+        <v>6441</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>106.81141916726</v>
+        <v>199.296307260011</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>48.02625827249426</v>
+        <v>44.74814526553797</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6.432357666853967</v>
+        <v>11.3713623426776</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0</v>
+        <v>0.5790820677898547</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.1643771023490958</v>
+        <v>-0.0588094547619904</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6441</v>
+        <v>6456</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>64.29630726001098</v>
+        <v>174.3404254651726</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>22.4</v>
+        <v>69.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.74814516042986</v>
+        <v>45.06543943175932</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.37136237195982</v>
+        <v>12.72017131145702</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5790820677898547</v>
+        <v>0.465397553291956</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0588094545425756</v>
+        <v>-0.8763030477556122</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6203</v>
+        <v>6236</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>64.29338740845755</v>
+        <v>106.81141916726</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>66.5</v>
+        <v>0</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.22684634401747</v>
+        <v>48.02625827249426</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.10187108980578</v>
+        <v>6.432357576696452</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7409178677236827</v>
+        <v>0</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.2475746664346269</v>
+        <v>-0.1643771023490958</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6194</v>
+        <v>6203</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>61.57642576571794</v>
+        <v>64.29338740845755</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>32.2</v>
+        <v>66.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>43.79891166427232</v>
+        <v>42.22684650027996</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.7776390732192</v>
+        <v>18.10187111781224</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3361047519028534</v>
+        <v>0.7409178677236827</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0631739355075661</v>
+        <v>-0.2475746664346269</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
